--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20047.08</v>
+        <v>19407.85</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>673.88</v>
+        <v>660.59</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8476.84</v>
+        <v>8323.120000000001</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35483.34</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>27119.25</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>65683.16</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41430.64</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>28088.19</v>
+        <v>28169.96</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>37692.53</v>
+        <v>37849.18</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45917.56</v>
+        <v>46307.26</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3452.55</v>
+        <v>3446.78</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19084.82</v>
+        <v>19319.71</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>443.19</v>
+        <v>448.64</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11556.92</v>
+        <v>11699.16</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>603876.53</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>33732.56</v>
+        <v>34181.63</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>278.43</v>
+        <v>282.14</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>45105.94</v>
+        <v>45694.56</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15522.32</v>
+        <v>15904.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>111.37</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>34790.04</v>
+        <v>35448.02</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3508.24</v>
+        <v>3519.28</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>202.19</v>
+        <v>202.82</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11109.43</v>
+        <v>11155.47</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>25615.72</v>
+        <v>25721.89</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1213.96</v>
+        <v>1216.48</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6415.07</v>
+        <v>6387.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1115,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1607,11 @@
           <t>77.854.171-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1672,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1737,11 @@
           <t>77.854.171-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2168,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -1546,7 +1546,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2233,7 +2237,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -749,7 +749,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +814,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +879,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -1408,7 +1408,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
